--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.79211950071074</v>
+        <v>6.628719418865495</v>
       </c>
       <c r="D2" t="n">
-        <v>40.45386344251872</v>
+        <v>6.573752809409293</v>
       </c>
       <c r="E2" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F2" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.64286405224587</v>
+        <v>4.979465408489954</v>
       </c>
       <c r="D3" t="n">
-        <v>30.35949093064787</v>
+        <v>4.933417276230279</v>
       </c>
       <c r="E3" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F3" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.69556544854363</v>
+        <v>5.31302938538834</v>
       </c>
       <c r="D4" t="n">
-        <v>49.98428473630879</v>
+        <v>8.12244626965018</v>
       </c>
       <c r="E4" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F4" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.4160903726647</v>
+        <v>5.430114685558014</v>
       </c>
       <c r="D5" t="n">
-        <v>32.80209454599905</v>
+        <v>5.330340363724846</v>
       </c>
       <c r="E5" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F5" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.76825027991175</v>
+        <v>4.18734067048566</v>
       </c>
       <c r="D6" t="n">
-        <v>47.51152730018856</v>
+        <v>7.720623186280641</v>
       </c>
       <c r="E6" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F6" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.48977882331825</v>
+        <v>1.704589058789215</v>
       </c>
       <c r="D7" t="n">
-        <v>26.78335853462775</v>
+        <v>4.352295761877009</v>
       </c>
       <c r="E7" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F7" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.24032345885321</v>
+        <v>5.564052562063647</v>
       </c>
       <c r="D8" t="n">
-        <v>38.95839583612131</v>
+        <v>6.330739323369714</v>
       </c>
       <c r="E8" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F8" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.20428236715762</v>
+        <v>6.533195884663113</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04557019018957</v>
+        <v>6.507405155905806</v>
       </c>
       <c r="E9" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F9" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>6.670832032063167</v>
+        <v>1.084010205210265</v>
       </c>
       <c r="D10" t="n">
-        <v>33.26148212837531</v>
+        <v>5.404990845860987</v>
       </c>
       <c r="E10" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F10" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.07026157005129</v>
+        <v>6.348917505133335</v>
       </c>
       <c r="D11" t="n">
-        <v>38.89812806163911</v>
+        <v>6.320945810016356</v>
       </c>
       <c r="E11" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F11" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>7.3824115301167</v>
+        <v>1.199641873643964</v>
       </c>
       <c r="D12" t="n">
-        <v>20.45243638119618</v>
+        <v>3.32352091194438</v>
       </c>
       <c r="E12" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F12" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>7.778174593052023</v>
+        <v>1.263953371370954</v>
       </c>
       <c r="D13" t="n">
-        <v>28.21746103669802</v>
+        <v>4.585337418463427</v>
       </c>
       <c r="E13" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F13" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.01515274552144</v>
+        <v>3.739962321147233</v>
       </c>
       <c r="D14" t="n">
-        <v>22.85833051575148</v>
+        <v>3.714478708809615</v>
       </c>
       <c r="E14" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F14" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>14.86829786253839</v>
+        <v>2.416098402662489</v>
       </c>
       <c r="D15" t="n">
-        <v>15.14394044592534</v>
+        <v>2.460890322462868</v>
       </c>
       <c r="E15" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F15" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>35.72319131536478</v>
+        <v>5.805018588746777</v>
       </c>
       <c r="D16" t="n">
-        <v>35.56137654860285</v>
+        <v>5.778723689147964</v>
       </c>
       <c r="E16" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F16" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34.53928072737328</v>
+        <v>5.612633118198159</v>
       </c>
       <c r="D17" t="n">
-        <v>34.4762436950779</v>
+        <v>5.602389600450159</v>
       </c>
       <c r="E17" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F17" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.32323594058209</v>
+        <v>5.74002584034459</v>
       </c>
       <c r="D18" t="n">
-        <v>35.85919238020954</v>
+        <v>5.827118761784051</v>
       </c>
       <c r="E18" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F18" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>12.07739330584744</v>
+        <v>1.96257641220021</v>
       </c>
       <c r="D19" t="n">
-        <v>12.15918921499727</v>
+        <v>1.975868247437057</v>
       </c>
       <c r="E19" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F19" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>33.58260487697622</v>
+        <v>5.457173292508636</v>
       </c>
       <c r="D20" t="n">
-        <v>33.5142030472081</v>
+        <v>5.446057995171317</v>
       </c>
       <c r="E20" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F20" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>33.06540073851224</v>
+        <v>5.373127620008239</v>
       </c>
       <c r="D21" t="n">
-        <v>33.23836054450706</v>
+        <v>5.401233588482397</v>
       </c>
       <c r="E21" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F21" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>37.05178527718913</v>
+        <v>6.020915107543234</v>
       </c>
       <c r="D22" t="n">
-        <v>37.14184073295051</v>
+        <v>6.035549119104458</v>
       </c>
       <c r="E22" t="n">
-        <v>11.67066114077574</v>
+        <v>1.896482435376058</v>
       </c>
       <c r="F22" t="n">
-        <v>9.231562689344219</v>
+        <v>1.500128937018436</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
